--- a/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado</t>
+          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 8,81</t>
+          <t>6,82; 9,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,82</t>
+          <t>6,49; 8,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,5</t>
+          <t>7,13; 9,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,52</t>
+          <t>6,54; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,64</t>
+          <t>7,22; 8,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,3</t>
+          <t>6,63; 8,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,84</t>
+          <t>6,82; 7,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,4</t>
+          <t>7,17; 8,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,32</t>
+          <t>7,03; 8,31</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,94</t>
+          <t>6,63; 7,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 8,32</t>
+          <t>7,05; 8,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,56</t>
+          <t>7,55; 9,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,66</t>
+          <t>6,31; 7,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,3</t>
+          <t>7,62; 9,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,24</t>
+          <t>6,01; 7,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 7,6</t>
+          <t>6,58; 7,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,64</t>
+          <t>7,51; 8,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,12</t>
+          <t>6,96; 8,18</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,16</t>
+          <t>6,76; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,13</t>
+          <t>6,75; 8,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,25</t>
+          <t>7,15; 9,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -917,27 +917,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,83</t>
+          <t>6,55; 7,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,24</t>
+          <t>7,04; 11,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,79</t>
+          <t>6,85; 7,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,75</t>
+          <t>6,84; 7,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 9,67</t>
+          <t>7,25; 9,64</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 7,81</t>
+          <t>6,24; 7,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,77</t>
+          <t>7,46; 10,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,51</t>
+          <t>7,27; 8,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,43</t>
+          <t>6,74; 8,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,27</t>
+          <t>7,03; 8,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,9</t>
+          <t>6,52; 7,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,82</t>
+          <t>6,71; 7,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,16</t>
+          <t>7,45; 9,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,1</t>
+          <t>7,15; 8,16</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,64</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,57</t>
+          <t>7,39; 8,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,62</t>
+          <t>7,68; 8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,6</t>
+          <t>6,85; 7,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,21</t>
+          <t>7,46; 8,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,91</t>
+          <t>6,82; 7,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,21</t>
+          <t>7,51; 8,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,03</t>
+          <t>7,38; 8,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,04</t>
+          <t>6,86; 8,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,76</t>
+          <t>6,61; 8,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,35</t>
+          <t>7,16; 9,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,51</t>
+          <t>6,57; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,69</t>
+          <t>7,22; 8,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,26</t>
+          <t>6,63; 8,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,69</t>
+          <t>6,8; 7,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,41</t>
+          <t>7,15; 8,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,31</t>
+          <t>7,06; 8,34</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,93</t>
+          <t>6,6; 7,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,29</t>
+          <t>7,08; 8,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 9,56</t>
+          <t>7,59; 9,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,7</t>
+          <t>6,26; 7,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 9,37</t>
+          <t>7,62; 9,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,22</t>
+          <t>6,02; 7,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,53</t>
+          <t>6,6; 7,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,61</t>
+          <t>7,5; 8,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 8,18</t>
+          <t>6,97; 8,22</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,17</t>
+          <t>6,74; 8,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,07</t>
+          <t>6,83; 8,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,28</t>
+          <t>7,08; 9,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,75</t>
+          <t>6,61; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,79</t>
+          <t>6,52; 7,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,04</t>
+          <t>6,93; 10,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,79</t>
+          <t>6,88; 7,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,72</t>
+          <t>6,8; 7,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,64</t>
+          <t>7,41; 9,76</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,83</t>
+          <t>6,21; 7,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,58</t>
+          <t>7,5; 10,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,59</t>
+          <t>7,29; 8,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,43</t>
+          <t>6,76; 8,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,3</t>
+          <t>6,99; 8,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,95</t>
+          <t>6,52; 7,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,92</t>
+          <t>6,68; 7,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,09</t>
+          <t>7,41; 9,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,16</t>
+          <t>7,11; 8,15</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,79; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,51</t>
+          <t>7,42; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,6</t>
+          <t>7,68; 8,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,57</t>
+          <t>6,83; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,23</t>
+          <t>7,38; 8,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,87</t>
+          <t>6,82; 7,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,48</t>
+          <t>6,91; 7,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,21</t>
+          <t>7,53; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,06</t>
+          <t>7,34; 8,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,88</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,79</t>
+          <t>6,55; 7,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,79</t>
+          <t>7,24; 8,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,43</t>
+          <t>6,67; 8,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,51</t>
+          <t>6,83; 8,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,7</t>
+          <t>6,54; 8,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,17</t>
+          <t>7,12; 9,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,69</t>
+          <t>6,85; 7,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,36</t>
+          <t>7,14; 8,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,34</t>
+          <t>7,02; 8,32</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,98</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,31</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,65</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,32</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,59</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,95</t>
+          <t>6,27; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,33</t>
+          <t>7,49; 9,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,5</t>
+          <t>5,96; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,63</t>
+          <t>6,63; 7,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 9,41</t>
+          <t>7,07; 8,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,2</t>
+          <t>7,54; 9,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,54</t>
+          <t>6,59; 7,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,6</t>
+          <t>7,5; 8,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,22</t>
+          <t>6,95; 8,12</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,13</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,15</t>
+          <t>6,62; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 8,05</t>
+          <t>6,53; 7,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,24</t>
+          <t>6,95; 11,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 7,77</t>
+          <t>6,74; 8,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,91</t>
+          <t>6,81; 8,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,88</t>
+          <t>7,14; 9,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,76</t>
+          <t>6,87; 7,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,73</t>
+          <t>6,83; 7,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,76</t>
+          <t>7,38; 9,67</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,58</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,36</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,88</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,98</t>
+          <t>6,76; 8,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 10,57</t>
+          <t>6,93; 8,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,65</t>
+          <t>6,55; 7,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,35</t>
+          <t>6,2; 7,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,3</t>
+          <t>7,52; 10,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,98</t>
+          <t>7,21; 8,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 7,95</t>
+          <t>6,66; 7,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,15</t>
+          <t>7,46; 9,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,15</t>
+          <t>7,16; 8,1</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,65</t>
+          <t>6,85; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,57</t>
+          <t>7,42; 8,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,59</t>
+          <t>6,85; 7,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,59</t>
+          <t>6,8; 7,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,17</t>
+          <t>7,37; 8,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,88</t>
+          <t>7,69; 8,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,47</t>
+          <t>6,95; 7,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,22</t>
+          <t>7,52; 8,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,04</t>
+          <t>7,37; 8,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,04</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7,72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,64</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.037340908480894</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.882041716830129</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.352511032538712</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.421902212181338</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7.47510381400492</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8.134915005881794</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>7.197331282248467</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>7.718080373297369</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.64021536735719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,55; 7,52</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,24; 8,64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,67; 8,3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6,83; 8,81</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,54; 8,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,12; 9,5</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,84</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 8,4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7,02; 8,32</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.550740577871885</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.240764052452452</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.665083808749242</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>6.828891546494457</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>6.544966957914457</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>7.124114694890497</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>6.854450217008075</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.141337241544544</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7.015860388481439</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.51988470093636</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.6421384487683</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.301454523880018</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.809405065964894</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8.816311875018521</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9.498997044797054</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>7.843449968268104</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>8.402028551129137</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.319295651316736</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,59</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,27; 7,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 9,3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 7,24</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,63; 7,94</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,07; 8,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 9,56</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 7,6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,5; 8,64</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 8,12</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.976943221920554</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.314814458475761</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.589865159497866</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.184516281764799</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7.654378268564266</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8.322251295730249</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7.062649640662495</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>7.997966637932195</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.45124904925103</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,13</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,07</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,31</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7,25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6.274345191295938</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.491554567201923</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.961671978714292</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>6.625751020506672</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.071226932588485</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>7.537531876489867</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.594504760241338</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.502335849822798</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6.945652769211406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,62; 7,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,53; 7,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 11,24</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6,74; 8,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 8,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 9,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,87; 7,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,83; 7,75</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>7,38; 9,67</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.657527065044315</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.297908879623421</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.242173762569045</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.93780776941608</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.316236931906294</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>9.560884753116087</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>7.596883290973749</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8.639567486995311</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8.120439751094134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,36</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,88</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,98</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.196423829248318</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.128460119909084</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8.197893878229037</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7.41515905174963</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.357046868354286</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8.07442665171013</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.308756885579626</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>7.25460932925383</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>8.14108075892597</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,76; 8,43</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,93; 8,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,55; 7,9</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6,2; 7,81</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 10,77</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,21; 8,51</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,66; 7,82</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 9,16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7,16; 8,1</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.62495083337635</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.533654565811308</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.954113335056009</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>6.742740614441162</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.807705760525758</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>7.136405230519578</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.871658937860412</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>6.826378547210536</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7.376265518047131</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.750411495975862</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.825208420413952</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.24205854850382</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.15715555482007</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.129096469161301</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>9.254509337118924</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.787742934296446</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>7.754599370280277</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.669789535086196</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.48039476305975</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.581998891871806</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.183757724165386</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7.004720038471663</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>8.362414616028094</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.879793655478013</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.240583192693517</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>7.983149693294939</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.614658576248049</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.758573426662191</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6.930605134929325</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6.549434507336215</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>6.204384419138496</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.517899923720623</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>7.205069572886642</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>6.663535761809824</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7.462227871403319</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.163681483110581</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.433594788475494</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.265799620447769</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.899727038553341</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.806594108372237</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>10.76962817091249</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>8.510601455436273</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.818439839658287</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.160916808010173</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8.096219587602535</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,21</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,91</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,64</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,57</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 8,62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 7,48</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>7.194568821393071</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.78669216585527</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.241462922260872</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7.201851859521645</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.793434878057755</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>8.090397653694831</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>7.197960668262682</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>7.789996458275741</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7.664646716399024</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.84520413204228</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7.421563673088825</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>6.853564913398673</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>6.797748991603733</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>7.373357305316943</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>7.690486094829057</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>6.950997366244207</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>7.522212523575002</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7.366378571170508</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.598708818335283</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.209710042480397</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.907356058578277</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.639725248553726</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.571050751942703</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8.616580532381422</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>7.482981390075063</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>8.213203967999696</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>8.032875538653988</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
